--- a/artfynd/A 54153-2021 artfynd.xlsx
+++ b/artfynd/A 54153-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54153-2021 artfynd.xlsx
+++ b/artfynd/A 54153-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102774060</v>
+        <v>102774072</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>599552.1977308857</v>
+        <v>599553</v>
       </c>
       <c r="R2" t="n">
-        <v>7027523.067063124</v>
+        <v>7027524</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +783,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102774072</v>
+        <v>102774060</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>599552.1977308857</v>
+        <v>599553</v>
       </c>
       <c r="R3" t="n">
-        <v>7027523.067063124</v>
+        <v>7027524</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54153-2021 artfynd.xlsx
+++ b/artfynd/A 54153-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102774072</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,8 +898,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102774060</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>